--- a/Input Data/ContractorList.xlsx
+++ b/Input Data/ContractorList.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DakotaRuhl\Documents\PS-DR\Input Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC7EFBE-D9BF-4066-955B-3873AD229BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49754D9-4447-4970-A4BB-DF32858FC04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E27B5980-8A07-4A5D-9AD2-51AB851DDA69}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E27B5980-8A07-4A5D-9AD2-51AB851DDA69}"/>
   </bookViews>
   <sheets>
     <sheet name="EntraID" sheetId="1" r:id="rId1"/>
     <sheet name="Paylocity" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,119 +40,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="54">
   <si>
     <t>UPN</t>
   </si>
   <si>
-    <t>rwilliams-sc@erock.com</t>
-  </si>
-  <si>
-    <t>rortega-sc@erock.com</t>
-  </si>
-  <si>
-    <t>twatts-sc@erock.com</t>
-  </si>
-  <si>
-    <t>tnorth-sc@erock.com</t>
-  </si>
-  <si>
-    <t>tnorris-sc@erock.com</t>
-  </si>
-  <si>
-    <t>vhall-sc@erock.com</t>
-  </si>
-  <si>
-    <t>aruiz-sc@erock.com</t>
-  </si>
-  <si>
-    <t>asuarez-sc@erock.com</t>
-  </si>
-  <si>
-    <t>aserrano-sc@erock.com</t>
-  </si>
-  <si>
-    <t>acruz-sc@erock.com</t>
-  </si>
-  <si>
-    <t>cingram-sc@erock.com</t>
-  </si>
-  <si>
-    <t>dcardenas-sc@erock.com</t>
-  </si>
-  <si>
-    <t>dcarns-sc@erock.com</t>
-  </si>
-  <si>
-    <t>dsmith-sc@erock.com</t>
-  </si>
-  <si>
-    <t>jmeleski-sc@erock.com</t>
-  </si>
-  <si>
-    <t>jpaz-sc@erock.com</t>
-  </si>
-  <si>
-    <t>lalatorre-sc@erock.com</t>
-  </si>
-  <si>
-    <t>martiga-sc@erock.com</t>
-  </si>
-  <si>
-    <t>Raven Williams (Contractor)</t>
-  </si>
-  <si>
-    <t>Ricardo Ortega (Contractor)</t>
-  </si>
-  <si>
-    <t>Teron Watts (Contractor)</t>
-  </si>
-  <si>
-    <t>Terrance North (Contractor)</t>
-  </si>
-  <si>
-    <t>Terrell Norris (Contractor)</t>
-  </si>
-  <si>
-    <t>Varrick Hall (Contractor)</t>
-  </si>
-  <si>
-    <t>Adrian Ruiz (Contractor)</t>
-  </si>
-  <si>
-    <t>Adrian Suarez (Contractor)</t>
-  </si>
-  <si>
-    <t>Alejandra Serrano (Contractor)</t>
-  </si>
-  <si>
-    <t>Andres Cruz (Contractor)</t>
-  </si>
-  <si>
-    <t>Carlton Ingram (Contractor)</t>
-  </si>
-  <si>
-    <t>Daniel Cardenas (Contractor)</t>
-  </si>
-  <si>
-    <t>David Carns (Contractor)</t>
-  </si>
-  <si>
-    <t>David Smith (Contractor)</t>
-  </si>
-  <si>
-    <t>James Meleski (Contractor)</t>
-  </si>
-  <si>
-    <t>Jessy Paz (Contractor)</t>
-  </si>
-  <si>
-    <t>Luis Alatorre (Contractor)</t>
-  </si>
-  <si>
-    <t>Marcus Artiga (Contractor)</t>
-  </si>
-  <si>
     <t>Job Title</t>
   </si>
   <si>
@@ -166,12 +57,6 @@
     <t>employeeType</t>
   </si>
   <si>
-    <t>Contractor</t>
-  </si>
-  <si>
-    <t>Aerotek</t>
-  </si>
-  <si>
     <t>CompanyName</t>
   </si>
   <si>
@@ -229,18 +114,6 @@
     <t>32Mega85Farseer!</t>
   </si>
   <si>
-    <t>29Grip71Shore!</t>
-  </si>
-  <si>
-    <t>92Steal16Orange!</t>
-  </si>
-  <si>
-    <t>82Jazz34Durango!</t>
-  </si>
-  <si>
-    <t>57Ample73Cauldron!</t>
-  </si>
-  <si>
     <t>25Jolted09Create!</t>
   </si>
   <si>
@@ -269,6 +142,66 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>PANEL1</t>
+  </si>
+  <si>
+    <t>BREAKER1</t>
+  </si>
+  <si>
+    <t>FANS</t>
+  </si>
+  <si>
+    <t>FUELSYS</t>
+  </si>
+  <si>
+    <t>ENC-DOOR</t>
+  </si>
+  <si>
+    <t>ENC-WALL</t>
+  </si>
+  <si>
+    <t>ENC-TAIL</t>
+  </si>
+  <si>
+    <t>ENGINE</t>
+  </si>
+  <si>
+    <t>HOOD_ENC1</t>
+  </si>
+  <si>
+    <t>HOOD_ENC2</t>
+  </si>
+  <si>
+    <t>HOOD_ENC3</t>
+  </si>
+  <si>
+    <t>QC-FAT</t>
+  </si>
+  <si>
+    <t>POWER1</t>
+  </si>
+  <si>
+    <t>POWER2</t>
+  </si>
+  <si>
+    <t>BC Device</t>
+  </si>
+  <si>
+    <t>Erock</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Warehouse Scanner Service Account</t>
+  </si>
+  <si>
+    <t>employeeId</t>
+  </si>
+  <si>
+    <t>svcaccount</t>
   </si>
 </sst>
 </file>
@@ -641,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DF31DA-6350-4B10-A53C-DB0067A330EB}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
@@ -650,842 +583,725 @@
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="10" max="10" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="K1" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="N1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="B2" t="str">
+        <f>A2 &amp; "@erock.com"</f>
+        <v>PANEL1@erock.com</v>
       </c>
       <c r="C2" t="str">
         <f>_xlfn.TEXTBEFORE(B2,"@")</f>
-        <v>rwilliams-sc</v>
-      </c>
-      <c r="D2" t="str">
+        <v>PANEL1</v>
+      </c>
+      <c r="D2" t="e">
         <f>_xlfn.TEXTBEFORE(A2," ")</f>
-        <v>Raven</v>
-      </c>
-      <c r="E2" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="E2" t="e">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2," "), " ")</f>
-        <v>Williams</v>
+        <v>#N/A</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>46258</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L2" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="B3" t="str">
+        <f t="shared" ref="B3:B15" si="0">A3 &amp; "@erock.com"</f>
+        <v>BREAKER1@erock.com</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C19" si="0">_xlfn.TEXTBEFORE(B3,"@")</f>
-        <v>rortega-sc</v>
-      </c>
-      <c r="D3" t="str">
+        <f t="shared" ref="C3:C15" si="1">_xlfn.TEXTBEFORE(B3,"@")</f>
+        <v>BREAKER1</v>
+      </c>
+      <c r="D3" t="e">
         <f>_xlfn.TEXTBEFORE(A3," ")</f>
-        <v>Ricardo</v>
-      </c>
-      <c r="E3" t="str">
-        <f t="shared" ref="E3:E19" si="1">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3," "), " ")</f>
-        <v>Ortega</v>
+        <v>#N/A</v>
+      </c>
+      <c r="E3" t="e">
+        <f t="shared" ref="E3:E15" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3," "), " ")</f>
+        <v>#N/A</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
         <v>46258</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>36</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" si="0"/>
+        <v>FANS@erock.com</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>twatts-sc</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" ref="D4:D19" si="2">_xlfn.TEXTBEFORE(A4," ")</f>
-        <v>Teron</v>
-      </c>
-      <c r="E4" t="str">
         <f t="shared" si="1"/>
-        <v>Watts</v>
+        <v>FANS</v>
+      </c>
+      <c r="D4" t="e">
+        <f t="shared" ref="D4:D15" si="3">_xlfn.TEXTBEFORE(A4," ")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E4" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
         <v>46258</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
         <v>50</v>
       </c>
-      <c r="M4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
+        <v>37</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>FUELSYS@erock.com</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>tnorth-sc</v>
-      </c>
-      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>FUELSYS</v>
+      </c>
+      <c r="D5" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E5" t="e">
         <f t="shared" si="2"/>
-        <v>Terrance</v>
-      </c>
-      <c r="E5" t="str">
-        <f t="shared" si="1"/>
-        <v>North</v>
+        <v>#N/A</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>46258</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="M5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
+        <v>38</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>ENC-DOOR@erock.com</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>tnorris-sc</v>
-      </c>
-      <c r="D6" t="str">
+        <f t="shared" si="1"/>
+        <v>ENC-DOOR</v>
+      </c>
+      <c r="D6" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="e">
         <f t="shared" si="2"/>
-        <v>Terrell</v>
-      </c>
-      <c r="E6" t="str">
-        <f t="shared" si="1"/>
-        <v>Norris</v>
+        <v>#N/A</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G6" s="1">
         <v>46258</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L6" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="M6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>ENC-WALL@erock.com</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>vhall-sc</v>
-      </c>
-      <c r="D7" t="str">
+        <f t="shared" si="1"/>
+        <v>ENC-WALL</v>
+      </c>
+      <c r="D7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="e">
         <f t="shared" si="2"/>
-        <v>Varrick</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" si="1"/>
-        <v>Hall</v>
+        <v>#N/A</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
         <v>46258</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>ENC-TAIL@erock.com</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>aruiz-sc</v>
-      </c>
-      <c r="D8" t="str">
+        <f t="shared" si="1"/>
+        <v>ENC-TAIL</v>
+      </c>
+      <c r="D8" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="e">
         <f t="shared" si="2"/>
-        <v>Adrian</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="1"/>
-        <v>Ruiz</v>
+        <v>#N/A</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>46258</v>
       </c>
       <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>41</v>
       </c>
-      <c r="I8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>ENGINE@erock.com</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="0"/>
-        <v>asuarez-sc</v>
-      </c>
-      <c r="D9" t="str">
+        <f t="shared" si="1"/>
+        <v>ENGINE</v>
+      </c>
+      <c r="D9" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E9" t="e">
         <f t="shared" si="2"/>
-        <v>Adrian</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="1"/>
-        <v>Suarez</v>
+        <v>#N/A</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>46258</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>HOOD_ENC1@erock.com</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="0"/>
-        <v>aserrano-sc</v>
-      </c>
-      <c r="D10" t="str">
+        <f t="shared" si="1"/>
+        <v>HOOD_ENC1</v>
+      </c>
+      <c r="D10" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="e">
         <f t="shared" si="2"/>
-        <v>Alejandra</v>
-      </c>
-      <c r="E10" t="str">
-        <f t="shared" si="1"/>
-        <v>Serrano</v>
+        <v>#N/A</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
         <v>46258</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L10" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
+        <v>43</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>HOOD_ENC2@erock.com</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="0"/>
-        <v>acruz-sc</v>
-      </c>
-      <c r="D11" t="str">
+        <f t="shared" si="1"/>
+        <v>HOOD_ENC2</v>
+      </c>
+      <c r="D11" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" t="e">
         <f t="shared" si="2"/>
-        <v>Andres</v>
-      </c>
-      <c r="E11" t="str">
-        <f t="shared" si="1"/>
-        <v>Cruz</v>
+        <v>#N/A</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1">
         <v>46258</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L11" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
+        <v>44</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>HOOD_ENC3@erock.com</v>
       </c>
       <c r="C12" t="str">
-        <f t="shared" si="0"/>
-        <v>cingram-sc</v>
-      </c>
-      <c r="D12" t="str">
+        <f t="shared" si="1"/>
+        <v>HOOD_ENC3</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" t="e">
         <f t="shared" si="2"/>
-        <v>Carlton</v>
-      </c>
-      <c r="E12" t="str">
-        <f t="shared" si="1"/>
-        <v>Ingram</v>
+        <v>#N/A</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>46258</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K12" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>45</v>
       </c>
-      <c r="L12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>QC-FAT@erock.com</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="1"/>
+        <v>QC-FAT</v>
+      </c>
+      <c r="D13" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="str">
-        <f t="shared" si="0"/>
-        <v>dcardenas-sc</v>
-      </c>
-      <c r="D13" t="str">
-        <f t="shared" si="2"/>
-        <v>Daniel</v>
-      </c>
-      <c r="E13" t="str">
-        <f t="shared" si="1"/>
-        <v>Cardenas</v>
-      </c>
-      <c r="F13" t="s">
-        <v>72</v>
       </c>
       <c r="G13" s="1">
         <v>46258</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>POWER1@erock.com</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="0"/>
-        <v>dcarns-sc</v>
-      </c>
-      <c r="D14" t="str">
+        <f t="shared" si="1"/>
+        <v>POWER1</v>
+      </c>
+      <c r="D14" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="e">
         <f t="shared" si="2"/>
-        <v>David</v>
-      </c>
-      <c r="E14" t="str">
-        <f t="shared" si="1"/>
-        <v>Carns</v>
+        <v>#N/A</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
         <v>46258</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K14" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="N14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>POWER2@erock.com</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="0"/>
-        <v>dsmith-sc</v>
-      </c>
-      <c r="D15" t="str">
+        <f t="shared" si="1"/>
+        <v>POWER2</v>
+      </c>
+      <c r="D15" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" t="e">
         <f t="shared" si="2"/>
-        <v>David</v>
-      </c>
-      <c r="E15" t="str">
-        <f t="shared" si="1"/>
-        <v>Smith</v>
+        <v>#N/A</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1">
         <v>46258</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="str">
-        <f t="shared" si="0"/>
-        <v>jmeleski-sc</v>
-      </c>
-      <c r="D16" t="str">
-        <f t="shared" si="2"/>
-        <v>James</v>
-      </c>
-      <c r="E16" t="str">
-        <f t="shared" si="1"/>
-        <v>Meleski</v>
-      </c>
-      <c r="F16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="1">
-        <v>46258</v>
-      </c>
-      <c r="H16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" t="s">
-        <v>45</v>
-      </c>
-      <c r="L16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="str">
-        <f t="shared" si="0"/>
-        <v>jpaz-sc</v>
-      </c>
-      <c r="D17" t="str">
-        <f t="shared" si="2"/>
-        <v>Jessy</v>
-      </c>
-      <c r="E17" t="str">
-        <f t="shared" si="1"/>
-        <v>Paz</v>
-      </c>
-      <c r="F17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="1">
-        <v>46258</v>
-      </c>
-      <c r="H17" t="s">
-        <v>41</v>
-      </c>
-      <c r="I17" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" t="s">
-        <v>45</v>
-      </c>
-      <c r="L17" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="str">
-        <f t="shared" si="0"/>
-        <v>lalatorre-sc</v>
-      </c>
-      <c r="D18" t="str">
-        <f t="shared" si="2"/>
-        <v>Luis</v>
-      </c>
-      <c r="E18" t="str">
-        <f t="shared" si="1"/>
-        <v>Alatorre</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="1">
-        <v>46258</v>
-      </c>
-      <c r="H18" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" t="s">
-        <v>64</v>
-      </c>
-      <c r="M18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="str">
-        <f t="shared" si="0"/>
-        <v>martiga-sc</v>
-      </c>
-      <c r="D19" t="str">
-        <f t="shared" si="2"/>
-        <v>Marcus</v>
-      </c>
-      <c r="E19" t="str">
-        <f t="shared" si="1"/>
-        <v>Artiga</v>
-      </c>
-      <c r="F19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="1">
-        <v>46258</v>
-      </c>
-      <c r="H19" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" t="s">
-        <v>45</v>
-      </c>
-      <c r="L19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19" t="s">
-        <v>75</v>
+        <v>50</v>
+      </c>
+      <c r="N15" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1505,16 +1321,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Input Data/ContractorList.xlsx
+++ b/Input Data/ContractorList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DakotaRuhl\Documents\PS-DR\Input Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49754D9-4447-4970-A4BB-DF32858FC04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F937D7D4-8FD2-4543-8F08-5620F7FF7484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E27B5980-8A07-4A5D-9AD2-51AB851DDA69}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E27B5980-8A07-4A5D-9AD2-51AB851DDA69}"/>
   </bookViews>
   <sheets>
     <sheet name="EntraID" sheetId="1" r:id="rId1"/>
@@ -162,9 +162,6 @@
     <t>ENC-WALL</t>
   </si>
   <si>
-    <t>ENC-TAIL</t>
-  </si>
-  <si>
     <t>ENGINE</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t>svcaccount</t>
+  </si>
+  <si>
+    <t>ENC-HAIL</t>
   </si>
 </sst>
 </file>
@@ -629,7 +629,7 @@
         <v>32</v>
       </c>
       <c r="N1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -659,13 +659,13 @@
         <v>46258</v>
       </c>
       <c r="H2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
-        <v>49</v>
-      </c>
       <c r="J2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K2" t="s">
         <v>7</v>
@@ -677,7 +677,7 @@
         <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -707,13 +707,13 @@
         <v>46258</v>
       </c>
       <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" t="s">
         <v>48</v>
       </c>
-      <c r="I3" t="s">
-        <v>49</v>
-      </c>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -722,10 +722,10 @@
         <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -755,13 +755,13 @@
         <v>46258</v>
       </c>
       <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" t="s">
         <v>48</v>
       </c>
-      <c r="I4" t="s">
-        <v>49</v>
-      </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
         <v>7</v>
@@ -770,10 +770,10 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -803,13 +803,13 @@
         <v>46258</v>
       </c>
       <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" t="s">
-        <v>49</v>
-      </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
         <v>7</v>
@@ -818,10 +818,10 @@
         <v>13</v>
       </c>
       <c r="M5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -851,13 +851,13 @@
         <v>46258</v>
       </c>
       <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
         <v>48</v>
       </c>
-      <c r="I6" t="s">
-        <v>49</v>
-      </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
         <v>7</v>
@@ -866,10 +866,10 @@
         <v>24</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -899,13 +899,13 @@
         <v>46258</v>
       </c>
       <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
         <v>48</v>
       </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
         <v>7</v>
@@ -914,23 +914,23 @@
         <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
-        <v>ENC-TAIL@erock.com</v>
+        <v>ENC-HAIL@erock.com</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="1"/>
-        <v>ENC-TAIL</v>
+        <v>ENC-HAIL</v>
       </c>
       <c r="D8" t="e">
         <f t="shared" si="3"/>
@@ -947,13 +947,13 @@
         <v>46258</v>
       </c>
       <c r="H8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" t="s">
         <v>48</v>
       </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
         <v>7</v>
@@ -962,15 +962,15 @@
         <v>16</v>
       </c>
       <c r="M8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
@@ -995,13 +995,13 @@
         <v>46258</v>
       </c>
       <c r="H9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" t="s">
         <v>48</v>
       </c>
-      <c r="I9" t="s">
-        <v>49</v>
-      </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
         <v>7</v>
@@ -1010,15 +1010,15 @@
         <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -1043,13 +1043,13 @@
         <v>46258</v>
       </c>
       <c r="H10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" t="s">
         <v>48</v>
       </c>
-      <c r="I10" t="s">
-        <v>49</v>
-      </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K10" t="s">
         <v>7</v>
@@ -1058,15 +1058,15 @@
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -1091,13 +1091,13 @@
         <v>46258</v>
       </c>
       <c r="H11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" t="s">
         <v>48</v>
       </c>
-      <c r="I11" t="s">
-        <v>49</v>
-      </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K11" t="s">
         <v>7</v>
@@ -1106,15 +1106,15 @@
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
@@ -1139,13 +1139,13 @@
         <v>46258</v>
       </c>
       <c r="H12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" t="s">
         <v>48</v>
       </c>
-      <c r="I12" t="s">
-        <v>49</v>
-      </c>
       <c r="J12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
         <v>7</v>
@@ -1154,15 +1154,15 @@
         <v>20</v>
       </c>
       <c r="M12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
@@ -1187,13 +1187,13 @@
         <v>46258</v>
       </c>
       <c r="H13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" t="s">
         <v>48</v>
       </c>
-      <c r="I13" t="s">
-        <v>49</v>
-      </c>
       <c r="J13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
         <v>7</v>
@@ -1202,15 +1202,15 @@
         <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
@@ -1235,13 +1235,13 @@
         <v>46258</v>
       </c>
       <c r="H14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" t="s">
         <v>48</v>
       </c>
-      <c r="I14" t="s">
-        <v>49</v>
-      </c>
       <c r="J14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
         <v>7</v>
@@ -1250,15 +1250,15 @@
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
@@ -1283,13 +1283,13 @@
         <v>46258</v>
       </c>
       <c r="H15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" t="s">
         <v>48</v>
       </c>
-      <c r="I15" t="s">
-        <v>49</v>
-      </c>
       <c r="J15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
         <v>7</v>
@@ -1298,10 +1298,10 @@
         <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
